--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2453,6 +2453,60 @@
       </c>
       <c r="K34" s="26" t="n"/>
       <c r="L34" s="25" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PlanetInspiredTraits</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>行星之子</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Klimter</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/klimter</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>46255</v>
+      </c>
+      <c r="G35" s="16" t="n">
+        <v>46255</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>无需前置</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>必须放第一层</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>images/klimter-planetinspiredtraits.png</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>人物特征</t>
         </is>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -254,7 +254,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WorksTable" displayName="WorksTable" ref="A1:L34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WorksTable" displayName="WorksTable" ref="A1:L35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A1:L34"/>
   <tableColumns count="12">
     <tableColumn id="1" name="状态"/>
@@ -2459,54 +2459,54 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>已发布</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>PlanetInspiredTraits</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="26" t="inlineStr">
         <is>
           <t>行星之子</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="26" t="inlineStr">
         <is>
           <t>Klimter</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="26" t="inlineStr">
         <is>
           <t>https://www.patreon.com/cw/klimter</t>
         </is>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="F35" s="27" t="n">
         <v>46255</v>
       </c>
-      <c r="G35" s="16" t="n">
+      <c r="G35" s="27" t="n">
         <v>46255</v>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="25" t="inlineStr">
         <is>
           <t>无需前置</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="25" t="inlineStr">
         <is>
           <t>必须放第一层</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="26" t="inlineStr">
         <is>
           <t>images/klimter-planetinspiredtraits.png</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
+      <c r="K35" s="26" t="inlineStr"/>
+      <c r="L35" s="25" t="inlineStr">
         <is>
           <t>人物特征</t>
         </is>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -94,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -178,6 +178,10 @@
     <xf numFmtId="165" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -254,8 +258,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WorksTable" displayName="WorksTable" ref="A1:L35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WorksTable" displayName="WorksTable" ref="A1:L36" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L36"/>
   <tableColumns count="12">
     <tableColumn id="1" name="状态"/>
     <tableColumn id="2" name="模组英文名"/>
@@ -471,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2145,10 +2149,8 @@
       <c r="F29" s="27" t="n">
         <v>46241</v>
       </c>
-      <c r="G29" s="27" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
+      <c r="G29" s="39" t="n">
+        <v>46248</v>
       </c>
       <c r="H29" s="25" t="inlineStr">
         <is>
@@ -2397,7 +2399,11 @@
           <t>images/klimter-foolishtrait.png</t>
         </is>
       </c>
-      <c r="K33" s="26" t="n"/>
+      <c r="K33" s="26" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/16GDYoljTlJduDEoxwykyuQ 提取码: db2z</t>
+        </is>
+      </c>
       <c r="L33" s="25" t="inlineStr">
         <is>
           <t>人物特征</t>
@@ -2507,6 +2513,59 @@
       </c>
       <c r="K35" s="26" t="inlineStr"/>
       <c r="L35" s="25" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BabyFeverTrait</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>宝宝控</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Klimter</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/klimter</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="n">
+        <v>46257</v>
+      </c>
+      <c r="G36" s="40" t="n">
+        <v>46257</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>无需前置</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>必须放第一层</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>images/klimter-babyfevertrait.png</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>人物特征</t>
         </is>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -2457,7 +2457,11 @@
           <t>images/klimter-parentaltrait.png</t>
         </is>
       </c>
-      <c r="K34" s="26" t="n"/>
+      <c r="K34" s="26" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1vhK_sEwzqs7OF2afKNI2sg 提取码: 93p1</t>
+        </is>
+      </c>
       <c r="L34" s="25" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2548,10 +2548,10 @@
           <t>https://www.patreon.com/cw/klimter</t>
         </is>
       </c>
-      <c r="F36" s="40" t="n">
+      <c r="F36" s="16" t="n">
         <v>46257</v>
       </c>
-      <c r="G36" s="40" t="n">
+      <c r="G36" s="16" t="n">
         <v>46257</v>
       </c>
       <c r="H36" t="inlineStr">
@@ -2569,7 +2569,61 @@
           <t>images/klimter-babyfevertrait.png</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BrattyTrait</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>爱耍性子</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Klimter</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/klimter</t>
+        </is>
+      </c>
+      <c r="F37" s="40" t="n">
+        <v>46260</v>
+      </c>
+      <c r="G37" s="40" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>无需前置</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>必须放第一层</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>images/klimter-brattytrait.png</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>人物特征</t>
         </is>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -2515,7 +2515,11 @@
           <t>images/klimter-planetinspiredtraits.png</t>
         </is>
       </c>
-      <c r="K35" s="26" t="inlineStr"/>
+      <c r="K35" s="26" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1Nb2iuFfmfMc4EKRCyP_0Rg 提取码: gn66</t>
+        </is>
+      </c>
       <c r="L35" s="25" t="inlineStr">
         <is>
           <t>人物特征</t>
@@ -2569,7 +2573,6 @@
           <t>images/klimter-babyfevertrait.png</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2627,6 +2627,60 @@
         </is>
       </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MoreHobbyTraits</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>更多爱好特征</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Klimter</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/klimter</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="n">
+        <v>46262</v>
+      </c>
+      <c r="G38" s="16" t="n">
+        <v>46262</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>无需前置</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>必须放第一层</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>images/klimter-morehobytraits.png</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>人物特征</t>
         </is>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2679,8 +2679,61 @@
           <t>images/klimter-morehobytraits.png</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Immortalitytrait</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>永不衰老</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Klimter</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/klimter</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="n">
+        <v>46262</v>
+      </c>
+      <c r="G39" s="16" t="n">
+        <v>46262</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>无需前置</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>必须放第一层</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>images/klimter-immortalitytrait.png</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
         <is>
           <t>人物特征</t>
         </is>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -932,7 +932,7 @@
         <v>46223</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>46223</v>
+        <v>46263</v>
       </c>
       <c r="H8" s="25" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>46257</v>
       </c>
       <c r="G36" s="16" t="n">
-        <v>46257</v>
+        <v>46263</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>46260</v>
       </c>
       <c r="G37" s="40" t="n">
-        <v>46260</v>
+        <v>46263</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>46262</v>
       </c>
       <c r="G38" s="16" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2732,7 +2732,6 @@
           <t>images/klimter-immortalitytrait.png</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -584,7 +584,7 @@
         <v>46237</v>
       </c>
       <c r="G2" s="27" t="n">
-        <v>46237</v>
+        <v>46264</v>
       </c>
       <c r="H2" s="25" t="inlineStr">
         <is>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -11,8 +11,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -569,7 +570,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -604,6 +605,12 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1127,7 +1134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="10" min="1" max="1"/>
@@ -3534,6 +3541,65 @@
       </c>
       <c r="L39" s="3" t="n"/>
       <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1" s="10">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>MaliciousTrait</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>捣蛋鬼特征</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Klimter</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/klimter</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>https://www.curseforge.com/sims4/mods/malicious-trait</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>46265</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>无需前置</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="inlineStr">
+        <is>
+          <t>必须放第一层</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>images/klimter-malicioustrait.png</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="n"/>
+      <c r="M40" s="13" t="inlineStr">
         <is>
           <t>人物特征</t>
         </is>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -11,9 +11,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -3404,7 +3403,7 @@
         <v>46260</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>46263</v>
+        <v>46267</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
@@ -3421,7 +3420,11 @@
           <t>images/klimter-brattytrait.png</t>
         </is>
       </c>
-      <c r="L37" s="3" t="n"/>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1PYCaYeJXJ6ETFA-y9BT7_g 提取码: xa2k</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
           <t>人物特征</t>
@@ -3605,6 +3608,7 @@
         </is>
       </c>
     </row>
+    <row r="41" ht="36" customHeight="1" s="10"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="A2:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -11,8 +11,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1133,7 +1134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="10" min="1" max="1"/>
@@ -3608,7 +3609,65 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="36" customHeight="1" s="10"/>
+    <row r="41" ht="36" customHeight="1" s="10">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>PatientTrait</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>耐心</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Klimter</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/klimter</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>https://www.curseforge.com/sims4/mods/patient-trait</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="n">
+        <v>46267</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>无需前置</t>
+        </is>
+      </c>
+      <c r="J41" s="13" t="inlineStr">
+        <is>
+          <t>必须放第一层</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>images/klimter-patienttrait.png</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="n"/>
+      <c r="M41" s="13" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="A2:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -11,9 +11,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1251,7 +1250,7 @@
         <v>46237</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>46264</v>
+        <v>46268</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="10" min="1" max="1"/>
@@ -3662,6 +3662,65 @@
       </c>
       <c r="L41" s="8" t="n"/>
       <c r="M41" s="13" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1" s="10">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Soft-HeartedTrait</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>心肠软弱</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Klimter</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/klimter</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>https://www.curseforge.com/sims4/mods/soft-hearted-trait</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="n">
+        <v>46269</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>46269</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>无需前置</t>
+        </is>
+      </c>
+      <c r="J42" s="13" t="inlineStr">
+        <is>
+          <t>必须放第一层</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>images/klimter-softheartedtrait.png</t>
+        </is>
+      </c>
+      <c r="L42" s="8" t="n"/>
+      <c r="M42" s="13" t="inlineStr">
         <is>
           <t>人物特征</t>
         </is>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -3483,7 +3483,11 @@
           <t>images/klimter-morehobytraits.png</t>
         </is>
       </c>
-      <c r="L38" s="3" t="n"/>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1NyT9GWICVfyLzQvtpjexMQ 提取码: hqnw</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
           <t>人物特征</t>
@@ -3542,7 +3546,11 @@
           <t>images/klimter-immortalitytrait.png</t>
         </is>
       </c>
-      <c r="L39" s="3" t="n"/>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/11FRdiNPX3V_eWde9lEdBag 提取码: zfn6</t>
+        </is>
+      </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="13" min="1" max="1"/>
@@ -3675,6 +3675,65 @@
       <c r="M43" s="23" t="inlineStr">
         <is>
           <t>人物特征</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1" s="22">
+      <c r="A44" s="23" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>High School Tea</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>高中吃瓜</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>JayESims</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/JayESims</t>
+        </is>
+      </c>
+      <c r="F44" s="24" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/JayESims/posts/jayesims-x-jaye-139297180</t>
+        </is>
+      </c>
+      <c r="G44" s="25" t="n">
+        <v>46272</v>
+      </c>
+      <c r="H44" s="25" t="n">
+        <v>46272</v>
+      </c>
+      <c r="I44" s="23" t="inlineStr">
+        <is>
+          <t>XML 注入器</t>
+        </is>
+      </c>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>无需放第一层</t>
+        </is>
+      </c>
+      <c r="K44" s="24" t="inlineStr">
+        <is>
+          <t>images/jayesims-high-school-tea.png</t>
+        </is>
+      </c>
+      <c r="L44" s="24" t="inlineStr"/>
+      <c r="M44" s="23" t="inlineStr">
+        <is>
+          <t>游戏玩法</t>
         </is>
       </c>
     </row>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
   <si>
     <t/>
   </si>
@@ -853,11 +853,6 @@
   <si>
     <r>
       <t>images/klimter-moreteentraits.png</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>链接: https://pan.baidu.com/s/1JjDQCozlFUyUgMHHT4fD-g 提取码: nm5w</t>
     </r>
   </si>
   <si>
@@ -1843,7 +1838,7 @@
     <xf numFmtId="301" fontId="5" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="301" fontId="6" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="301" fontId="6" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3322,7 +3317,7 @@
         <v>46244</v>
       </c>
       <c r="H30" s="7">
-        <v>46251</v>
+        <v>46272</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>31</v>
@@ -3345,10 +3340,10 @@
         <v>15</v>
       </c>
       <c r="B31" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>170</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>171</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>
@@ -3357,7 +3352,7 @@
         <v>29</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G31" s="7">
         <v>46246</v>
@@ -3372,10 +3367,10 @@
         <v>32</v>
       </c>
       <c r="K31" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="L31" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="M31" s="5" t="s">
         <v>35</v>
@@ -3386,10 +3381,10 @@
         <v>15</v>
       </c>
       <c r="B32" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>28</v>
@@ -3398,7 +3393,7 @@
         <v>29</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G32" s="7">
         <v>46248</v>
@@ -3413,10 +3408,10 @@
         <v>32</v>
       </c>
       <c r="K32" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="L32" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="M32" s="5" t="s">
         <v>35</v>
@@ -3427,10 +3422,10 @@
         <v>15</v>
       </c>
       <c r="B33" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>28</v>
@@ -3439,7 +3434,7 @@
         <v>29</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G33" s="7">
         <v>46250</v>
@@ -3454,10 +3449,10 @@
         <v>32</v>
       </c>
       <c r="K33" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="L33" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="M33" s="5" t="s">
         <v>35</v>
@@ -3468,10 +3463,10 @@
         <v>15</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>28</v>
@@ -3480,7 +3475,7 @@
         <v>29</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G34" s="7">
         <v>46253</v>
@@ -3495,10 +3490,10 @@
         <v>32</v>
       </c>
       <c r="K34" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="L34" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>35</v>
@@ -3509,10 +3504,10 @@
         <v>15</v>
       </c>
       <c r="B35" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>28</v>
@@ -3521,7 +3516,7 @@
         <v>29</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G35" s="7">
         <v>46255</v>
@@ -3536,10 +3531,10 @@
         <v>32</v>
       </c>
       <c r="K35" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="L35" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>35</v>
@@ -3550,10 +3545,10 @@
         <v>15</v>
       </c>
       <c r="B36" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>28</v>
@@ -3562,7 +3557,7 @@
         <v>29</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G36" s="7">
         <v>46257</v>
@@ -3577,10 +3572,10 @@
         <v>32</v>
       </c>
       <c r="K36" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="L36" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="M36" s="5" t="s">
         <v>35</v>
@@ -3591,10 +3586,10 @@
         <v>15</v>
       </c>
       <c r="B37" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>28</v>
@@ -3603,7 +3598,7 @@
         <v>29</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G37" s="7">
         <v>46260</v>
@@ -3618,10 +3613,10 @@
         <v>32</v>
       </c>
       <c r="K37" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="L37" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="M37" s="5" t="s">
         <v>35</v>
@@ -3632,10 +3627,10 @@
         <v>15</v>
       </c>
       <c r="B38" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>205</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>206</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>28</v>
@@ -3644,7 +3639,7 @@
         <v>29</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G38" s="7">
         <v>46262</v>
@@ -3659,10 +3654,10 @@
         <v>32</v>
       </c>
       <c r="K38" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="L38" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="L38" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="M38" s="5" t="s">
         <v>35</v>
@@ -3673,10 +3668,10 @@
         <v>15</v>
       </c>
       <c r="B39" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>28</v>
@@ -3685,7 +3680,7 @@
         <v>29</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G39" s="7">
         <v>46262</v>
@@ -3700,10 +3695,10 @@
         <v>32</v>
       </c>
       <c r="K39" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="L39" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="L39" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="M39" s="5" t="s">
         <v>35</v>
@@ -3714,10 +3709,10 @@
         <v>15</v>
       </c>
       <c r="B40" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C40" s="10" t="s">
         <v>215</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>216</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>28</v>
@@ -3726,7 +3721,7 @@
         <v>29</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G40" s="11">
         <v>46265</v>
@@ -3741,10 +3736,10 @@
         <v>32</v>
       </c>
       <c r="K40" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="L40" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="L40" s="10" t="s">
-        <v>219</v>
       </c>
       <c r="M40" s="9" t="s">
         <v>35</v>
@@ -3755,10 +3750,10 @@
         <v>15</v>
       </c>
       <c r="B41" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="C41" s="10" t="s">
         <v>220</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>221</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>28</v>
@@ -3767,7 +3762,7 @@
         <v>29</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G41" s="11">
         <v>46267</v>
@@ -3782,7 +3777,7 @@
         <v>32</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L41" s="10" t="s"/>
       <c r="M41" s="9" t="s">
@@ -3794,10 +3789,10 @@
         <v>15</v>
       </c>
       <c r="B42" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="C42" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>28</v>
@@ -3806,7 +3801,7 @@
         <v>29</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G42" s="11">
         <v>46269</v>
@@ -3821,7 +3816,7 @@
         <v>32</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L42" s="10" t="s"/>
       <c r="M42" s="9" t="s">
@@ -3833,10 +3828,10 @@
         <v>15</v>
       </c>
       <c r="B43" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C43" s="13" t="s">
         <v>228</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>229</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>28</v>
@@ -3845,7 +3840,7 @@
         <v>29</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G43" s="14">
         <v>46271</v>
@@ -3860,7 +3855,7 @@
         <v>32</v>
       </c>
       <c r="K43" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L43" s="13" t="s"/>
       <c r="M43" s="12" t="s">
@@ -3872,10 +3867,10 @@
         <v>15</v>
       </c>
       <c r="B44" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="C44" s="13" t="s">
         <v>232</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>233</v>
       </c>
       <c r="D44" s="13" t="s">
         <v>93</v>
@@ -3884,7 +3879,7 @@
         <v>94</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G44" s="14">
         <v>46272</v>
@@ -3899,7 +3894,7 @@
         <v>22</v>
       </c>
       <c r="K44" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L44" s="13" t="s"/>
       <c r="M44" s="12" t="s">

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -583,7 +583,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -665,6 +665,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0"/>
@@ -790,7 +791,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WorksTable" displayName="WorksTable" ref="A1:L36" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WorksTable" displayName="WorksTable" ref="A1:N45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A1:L36"/>
   <tableColumns count="12">
     <tableColumn id="1" name="状态"/>
@@ -1007,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="18" min="1" max="1"/>
@@ -1020,6 +1021,7 @@
     <col width="40" customWidth="1" style="18" min="11" max="11"/>
     <col width="38" customWidth="1" style="18" min="12" max="12"/>
     <col width="14" customWidth="1" style="18" min="13" max="13"/>
+    <col width="16" customWidth="1" style="27" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customFormat="1" customHeight="1" s="18">
@@ -1088,6 +1090,11 @@
           <t>类别</t>
         </is>
       </c>
+      <c r="N1" s="19" t="inlineStr">
+        <is>
+          <t>上新日期</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="20" t="inlineStr">
@@ -1151,6 +1158,9 @@
           <t>职业</t>
         </is>
       </c>
+      <c r="N2" s="22" t="n">
+        <v>46237</v>
+      </c>
     </row>
     <row r="3" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A3" s="20" t="inlineStr">
@@ -1214,6 +1224,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N3" s="22" t="n">
+        <v>46234</v>
+      </c>
     </row>
     <row r="4" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A4" s="20" t="inlineStr">
@@ -1277,6 +1290,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N4" s="22" t="n">
+        <v>46232</v>
+      </c>
     </row>
     <row r="5" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A5" s="20" t="inlineStr">
@@ -1340,6 +1356,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N5" s="22" t="n">
+        <v>46230</v>
+      </c>
     </row>
     <row r="6" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="20" t="inlineStr">
@@ -1403,6 +1422,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N6" s="22" t="n">
+        <v>46227</v>
+      </c>
     </row>
     <row r="7" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A7" s="20" t="inlineStr">
@@ -1466,6 +1488,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N7" s="22" t="n">
+        <v>46225</v>
+      </c>
     </row>
     <row r="8" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A8" s="20" t="inlineStr">
@@ -1529,6 +1554,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N8" s="22" t="n">
+        <v>46223</v>
+      </c>
     </row>
     <row r="9" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A9" s="20" t="inlineStr">
@@ -1592,6 +1620,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N9" s="22" t="n">
+        <v>46220</v>
+      </c>
     </row>
     <row r="10" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A10" s="20" t="inlineStr">
@@ -1655,6 +1686,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N10" s="22" t="n">
+        <v>46219</v>
+      </c>
     </row>
     <row r="11" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A11" s="20" t="inlineStr">
@@ -1718,6 +1752,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N11" s="22" t="n">
+        <v>46216</v>
+      </c>
     </row>
     <row r="12" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A12" s="20" t="inlineStr">
@@ -1781,6 +1818,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N12" s="22" t="n">
+        <v>46213</v>
+      </c>
     </row>
     <row r="13" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A13" s="20" t="inlineStr">
@@ -1844,6 +1884,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N13" s="22" t="n">
+        <v>46211</v>
+      </c>
     </row>
     <row r="14" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A14" s="20" t="inlineStr">
@@ -1906,6 +1949,9 @@
         <is>
           <t>人物特征</t>
         </is>
+      </c>
+      <c r="N14" s="22" t="n">
+        <v>46209</v>
       </c>
     </row>
     <row r="15" ht="36" customFormat="1" customHeight="1" s="18">
@@ -1966,6 +2012,9 @@
           <t>游戏玩法</t>
         </is>
       </c>
+      <c r="N15" s="22" t="n">
+        <v>46206</v>
+      </c>
     </row>
     <row r="16" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A16" s="20" t="inlineStr">
@@ -2025,6 +2074,9 @@
           <t>职业</t>
         </is>
       </c>
+      <c r="N16" s="22" t="n">
+        <v>46206</v>
+      </c>
     </row>
     <row r="17" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A17" s="20" t="inlineStr">
@@ -2084,6 +2136,9 @@
           <t>游戏玩法</t>
         </is>
       </c>
+      <c r="N17" s="22" t="n">
+        <v>46205</v>
+      </c>
     </row>
     <row r="18" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A18" s="20" t="inlineStr">
@@ -2143,6 +2198,9 @@
           <t>职业</t>
         </is>
       </c>
+      <c r="N18" s="22" t="n">
+        <v>46205</v>
+      </c>
     </row>
     <row r="19" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A19" s="20" t="inlineStr">
@@ -2202,6 +2260,9 @@
           <t>游戏玩法</t>
         </is>
       </c>
+      <c r="N19" s="22" t="n">
+        <v>46204</v>
+      </c>
     </row>
     <row r="20" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A20" s="20" t="inlineStr">
@@ -2261,6 +2322,9 @@
           <t>游戏玩法</t>
         </is>
       </c>
+      <c r="N20" s="22" t="n">
+        <v>46203</v>
+      </c>
     </row>
     <row r="21" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A21" s="20" t="inlineStr">
@@ -2320,6 +2384,9 @@
           <t>游戏玩法</t>
         </is>
       </c>
+      <c r="N21" s="22" t="n">
+        <v>46203</v>
+      </c>
     </row>
     <row r="22" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A22" s="20" t="inlineStr">
@@ -2379,6 +2446,9 @@
           <t>游戏玩法</t>
         </is>
       </c>
+      <c r="N22" s="22" t="n">
+        <v>46203</v>
+      </c>
     </row>
     <row r="23" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A23" s="20" t="inlineStr">
@@ -2438,6 +2508,9 @@
           <t>游戏玩法</t>
         </is>
       </c>
+      <c r="N23" s="22" t="n">
+        <v>46203</v>
+      </c>
     </row>
     <row r="24" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A24" s="20" t="inlineStr">
@@ -2497,6 +2570,9 @@
           <t>游戏玩法</t>
         </is>
       </c>
+      <c r="N24" s="22" t="n">
+        <v>46203</v>
+      </c>
     </row>
     <row r="25" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A25" s="20" t="inlineStr">
@@ -2556,6 +2632,9 @@
           <t>覆盖替换</t>
         </is>
       </c>
+      <c r="N25" s="22" t="n">
+        <v>46203</v>
+      </c>
     </row>
     <row r="26" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A26" s="20" t="inlineStr">
@@ -2615,6 +2694,9 @@
           <t>用地特征</t>
         </is>
       </c>
+      <c r="N26" s="22" t="n">
+        <v>46203</v>
+      </c>
     </row>
     <row r="27" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A27" s="20" t="inlineStr">
@@ -2674,6 +2756,9 @@
           <t>游戏玩法</t>
         </is>
       </c>
+      <c r="N27" s="22" t="n">
+        <v>46203</v>
+      </c>
     </row>
     <row r="28" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A28" s="20" t="inlineStr">
@@ -2737,6 +2822,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N28" s="22" t="n">
+        <v>46239</v>
+      </c>
     </row>
     <row r="29" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A29" s="20" t="inlineStr">
@@ -2800,6 +2888,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N29" s="22" t="n">
+        <v>46241</v>
+      </c>
     </row>
     <row r="30" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A30" s="20" t="inlineStr">
@@ -2863,6 +2954,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N30" s="22" t="n">
+        <v>46244</v>
+      </c>
     </row>
     <row r="31" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A31" s="20" t="inlineStr">
@@ -2926,6 +3020,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N31" s="22" t="n">
+        <v>46246</v>
+      </c>
     </row>
     <row r="32" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A32" s="20" t="inlineStr">
@@ -2989,6 +3086,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N32" s="22" t="n">
+        <v>46248</v>
+      </c>
     </row>
     <row r="33" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A33" s="20" t="inlineStr">
@@ -3052,6 +3152,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N33" s="22" t="n">
+        <v>46250</v>
+      </c>
     </row>
     <row r="34" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A34" s="20" t="inlineStr">
@@ -3115,6 +3218,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N34" s="22" t="n">
+        <v>46253</v>
+      </c>
     </row>
     <row r="35" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A35" s="20" t="inlineStr">
@@ -3178,6 +3284,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N35" s="22" t="n">
+        <v>46255</v>
+      </c>
     </row>
     <row r="36" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A36" s="20" t="inlineStr">
@@ -3241,6 +3350,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N36" s="22" t="n">
+        <v>46257</v>
+      </c>
     </row>
     <row r="37" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A37" s="20" t="inlineStr">
@@ -3304,6 +3416,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N37" s="22" t="n">
+        <v>46260</v>
+      </c>
     </row>
     <row r="38" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A38" s="20" t="inlineStr">
@@ -3367,6 +3482,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N38" s="22" t="n">
+        <v>46262</v>
+      </c>
     </row>
     <row r="39" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A39" s="20" t="inlineStr">
@@ -3430,6 +3548,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N39" s="22" t="n">
+        <v>46262</v>
+      </c>
     </row>
     <row r="40" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A40" s="9" t="inlineStr">
@@ -3493,6 +3614,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N40" s="23" t="n">
+        <v>46265</v>
+      </c>
     </row>
     <row r="41" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A41" s="9" t="inlineStr">
@@ -3556,6 +3680,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N41" s="23" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="42" ht="36" customFormat="1" customHeight="1" s="18">
       <c r="A42" s="9" t="inlineStr">
@@ -3615,6 +3742,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N42" s="23" t="n">
+        <v>46269</v>
+      </c>
     </row>
     <row r="43" ht="36" customFormat="1" customHeight="1" s="24">
       <c r="A43" s="12" t="inlineStr">
@@ -3674,6 +3804,9 @@
           <t>人物特征</t>
         </is>
       </c>
+      <c r="N43" s="25" t="n">
+        <v>46271</v>
+      </c>
     </row>
     <row r="44" ht="36" customFormat="1" customHeight="1" s="24">
       <c r="A44" s="12" t="inlineStr">
@@ -3733,6 +3866,9 @@
           <t>游戏玩法</t>
         </is>
       </c>
+      <c r="N44" s="25" t="n">
+        <v>46272</v>
+      </c>
     </row>
     <row r="45" ht="36" customFormat="1" customHeight="1" s="26">
       <c r="A45" s="20" t="inlineStr">
@@ -3791,6 +3927,9 @@
         <is>
           <t>游戏玩法</t>
         </is>
+      </c>
+      <c r="N45" s="22" t="n">
+        <v>46274</v>
       </c>
     </row>
   </sheetData>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -3750,7 +3750,11 @@
           <t>images/klimter-softheartedtrait.png</t>
         </is>
       </c>
-      <c r="L42" s="10" t="inlineStr"/>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1IwpX1_AAlImKcdtIlp1Qgw?pwd=asba 提取码: asba</t>
+        </is>
+      </c>
       <c r="M42" s="9" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -3816,7 +3816,11 @@
           <t>images/klimter-temptingtrait.png</t>
         </is>
       </c>
-      <c r="L43" s="13" t="inlineStr"/>
+      <c r="L43" s="13" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1ErMmagLQ17IYLLQqYOMZGQ?pwd=eugh 提取码: eugh</t>
+        </is>
+      </c>
       <c r="M43" s="12" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -3799,7 +3799,7 @@
         <v>46275</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="G6" s="21" t="n">
-        <v>46227</v>
+        <v>46278</v>
       </c>
       <c r="H6" s="21" t="n">
         <v>46227</v>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -2180,7 +2180,11 @@
           <t>https://wickedpixxel.com/</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>https://wickedpixxel.com/sexy-gigs-v21-2/</t>
+        </is>
+      </c>
       <c r="G18" s="21" t="n">
         <v>46205</v>
       </c>

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>https://wickedpixxel.com/sexy-gigs-v21-2/</t>
+          <t>https://www.patreon.com/wickedpixxel/posts/sexy-gigs-v21-2-156917522</t>
         </is>
       </c>
       <c r="G18" s="21" t="n">

--- a/作品信息.xlsx
+++ b/作品信息.xlsx
@@ -4013,7 +4013,7 @@
       <c r="L46" s="6" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>游戏玩法</t>
+          <t>人物特征</t>
         </is>
       </c>
       <c r="N46" s="21" t="n">
